--- a/data.mn/public/datasets/nso-deaths-monthly.xlsx
+++ b/data.mn/public/datasets/nso-deaths-monthly.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="English" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Монгол" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1705,4 +1706,1304 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B128"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>сар</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>нас_баралт</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2016-01</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2016-02</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1372</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2016-03</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1457</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2016-04</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2016-05</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2016-06</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1297</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1355</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2016-09</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1348</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1286</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2017-02</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1206</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1362</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2017-09</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1360</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1378</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>1411</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1370</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>1486</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>1375</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1432</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1367</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1533</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1391</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="B35" t="n">
+        <v>1461</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="B37" t="n">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1358</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>1431</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1508</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>1280</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>1410</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>1542</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1266</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="B49" t="n">
+        <v>1674</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="B50" t="n">
+        <v>1366</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="B51" t="n">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="B52" t="n">
+        <v>1292</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1310</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1288</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="B55" t="n">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="B56" t="n">
+        <v>1402</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="B57" t="n">
+        <v>1331</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="B59" t="n">
+        <v>1427</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1278</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="B61" t="n">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1484</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1715</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>1819</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1678</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>2302</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>1950</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>1785</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>1424</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>1438</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>1490</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1485</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>1671</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1430</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1336</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1587</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1344</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>1519</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>1442</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1347</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>1691</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1398</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>1545</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1506</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>1504</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>1592</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>1706</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="B111" t="n">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="B112" t="n">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="B113" t="n">
+        <v>1496</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="B114" t="n">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="B115" t="n">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="B116" t="n">
+        <v>1493</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="B117" t="n">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="B118" t="n">
+        <v>1551</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="B119" t="n">
+        <v>1572</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="B120" t="n">
+        <v>1550</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="B121" t="n">
+        <v>1622</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="B122" t="n">
+        <v>1473</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="B123" t="n">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="B124" t="n">
+        <v>1725</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="B125" t="n">
+        <v>1364</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="B126" t="n">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="B127" t="n">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="B128" t="n">
+        <v>1637</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.mn/public/datasets/nso-deaths-monthly.xlsx
+++ b/data.mn/public/datasets/nso-deaths-monthly.xlsx
@@ -414,12 +414,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -1701,6 +1697,26 @@
       </c>
       <c r="B128" t="n">
         <v>1637</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1570</v>
       </c>
     </row>
   </sheetData>
@@ -1714,12 +1730,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B128"/>
+  <dimension ref="A1:B130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -3001,6 +3013,26 @@
       </c>
       <c r="B128" t="n">
         <v>1637</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B129" t="n">
+        <v>1403</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="B130" t="n">
+        <v>1570</v>
       </c>
     </row>
   </sheetData>
